--- a/output/pdf_financials_xlsx/BEX.xlsx
+++ b/output/pdf_financials_xlsx/BEX.xlsx
@@ -5285,31 +5285,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>22.092665</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.9340079999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.200387</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.597552</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.662543</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.668326</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.753063</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.826949</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.112247</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
@@ -5321,10 +5321,10 @@
         <v>0</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.847096</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.4852</v>
       </c>
     </row>
     <row r="93">
@@ -6589,46 +6589,46 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>2.597917</v>
+        <v>-0.407505</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.862188</v>
+        <v>-1.468664</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>3.43854</v>
+        <v>1.863068</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>3.724633</v>
+        <v>2.925834</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.025258</v>
+        <v>-0.79029</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.672471</v>
+        <v>0.077239</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.242728</v>
+        <v>-0.844155</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.34265</v>
+        <v>-0.463342</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>1.594683</v>
+        <v>-1.834218</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>-0.198418</v>
+        <v>-1.8523</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.869775</v>
+        <v>-2.242829</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>1.936682</v>
+        <v>-2.674764</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>2.237651</v>
+        <v>-1.842862</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>1.176084</v>
+        <v>-2.481525</v>
       </c>
     </row>
     <row r="119">
@@ -9172,7 +9172,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>22.092665</v>
       </c>
@@ -25234,7 +25238,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E210" s="5" t="n">
         <v>-3.005422</v>
       </c>
@@ -30798,7 +30806,11 @@
           <t>Grants received for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BEX.xlsx
+++ b/output/pdf_financials_xlsx/BEX.xlsx
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.272547</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.093374</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-11.81156</v>
+        <v>-12.084107</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.87265</v>
+        <v>-1.966024</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-4.798503</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-11.81156</v>
+        <v>-12.084107</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.87265</v>
+        <v>-1.966024</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-4.798503</v>
@@ -2263,46 +2263,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.04474</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.110408</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.05055</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.14837</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.146733</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.180264</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.065665</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.131324</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.197542</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.340949</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.177508</v>
       </c>
     </row>
     <row r="35">
@@ -2361,46 +2361,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.04474</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.110408</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.05055</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.14837</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.146733</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.180264</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.065665</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.131324</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.197542</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.340949</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.177508</v>
       </c>
     </row>
     <row r="37">
@@ -2949,31 +2949,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.154698</v>
+        <v>0.154697</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>8.812766999999999</v>
+        <v>8.768027</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>6.76223</v>
+        <v>6.651822</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>5.442091</v>
+        <v>5.391541</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.786022</v>
+        <v>3.637652</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.251578</v>
+        <v>2.104845</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.386838</v>
+        <v>1.206574</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.313852</v>
+        <v>3.248187</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.147127</v>
+        <v>2.015803</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -2985,10 +2985,10 @@
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.530793</v>
+        <v>3.189844</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.390337</v>
+        <v>1.212829</v>
       </c>
     </row>
     <row r="49">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -16364,7 +16364,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -40266,7 +40266,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E394" s="5" t="n">

--- a/output/pdf_financials_xlsx/BEX.xlsx
+++ b/output/pdf_financials_xlsx/BEX.xlsx
@@ -6304,25 +6304,25 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.0048</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -6331,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.026854</v>
       </c>
       <c r="O112" s="3" t="n">
         <v>0</v>
@@ -25434,7 +25434,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -30388,7 +30392,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -31504,7 +31512,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BEX.xlsx
+++ b/output/pdf_financials_xlsx/BEX.xlsx
@@ -628,20 +628,14 @@
       <c r="J5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>0</v>
@@ -738,20 +732,14 @@
       <c r="J7" s="3" t="n">
         <v>0.04</v>
       </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>0.061854</v>
@@ -793,20 +781,14 @@
       <c r="J8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>0</v>
@@ -848,20 +830,14 @@
       <c r="J9" s="3" t="n">
         <v>0.09853000000000001</v>
       </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>0.234449</v>
@@ -903,20 +879,14 @@
       <c r="J10" s="3" t="n">
         <v>2.912752</v>
       </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>5.535664</v>
@@ -1013,20 +983,14 @@
       <c r="J12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1068,20 +1032,14 @@
       <c r="J13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>-0</v>
@@ -1123,20 +1081,14 @@
       <c r="J14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>0</v>
@@ -1178,20 +1130,14 @@
       <c r="J15" s="3" t="n">
         <v>0.012</v>
       </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>0</v>
@@ -1233,20 +1179,14 @@
       <c r="J16" s="3" t="n">
         <v>3.435219</v>
       </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K16" s="3" t="n">
+        <v>-1.062007</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>-6.138987</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>-2.890827</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-3.383148</v>
@@ -1262,13 +1202,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2.885994</v>
+        <v>-0.40375</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.235157</v>
+        <v>0.235157</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.293456</v>
+        <v>-0.293456</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1288,20 +1228,14 @@
       <c r="J17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-0</v>
@@ -1497,20 +1431,14 @@
       <c r="J20" s="3" t="n">
         <v>3.435219</v>
       </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K20" s="3" t="n">
+        <v>-1.062007</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>-6.138987</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>-2.890827</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-3.383148</v>
@@ -1552,20 +1480,14 @@
       <c r="J21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>0</v>
@@ -1607,20 +1529,14 @@
       <c r="J22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>0</v>
@@ -1908,20 +1824,14 @@
       <c r="J27" s="3" t="n">
         <v>3.435219</v>
       </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K27" s="3" t="n">
+        <v>-1.062007</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>-6.138987</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>-2.890827</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-3.383148</v>
@@ -1958,31 +1868,25 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.023477</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.062022</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0.069065</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0.074878</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>0.076028</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.029934</v>
       </c>
     </row>
     <row r="29">
@@ -2013,31 +1917,25 @@
         <v>2.073348</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.330133</v>
+        <v>-1.306656</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>3.435219</v>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.497241</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>-0.992942</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>-6.064109</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>-2.814799</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.383148</v>
+        <v>-3.308348</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.424169</v>
+        <v>-0.394235</v>
       </c>
     </row>
     <row r="30">
@@ -2124,7 +2022,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-24.43363958698089</v>
+        <v>-3.418261432020834</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-12.55744533148212</v>
@@ -2150,20 +2048,14 @@
       <c r="J31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -5728,25 +5620,25 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.023477</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.062022</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.069065</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.074878</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.076028</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.029934</v>
       </c>
     </row>
     <row r="101">
@@ -7515,7 +7407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R403"/>
+  <dimension ref="A1:R406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -24022,7 +23914,11 @@
           <t>Depreciation and amortization expense</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -30306,7 +30202,11 @@
           <t>Acquisition of long term investments in private placement</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -31078,7 +30978,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -31766,7 +31670,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E291" s="5" t="n">
         <v>-2.592415</v>
       </c>
@@ -33224,7 +33132,11 @@
           <t>Depreciation and amortization expense</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -34654,25 +34566,27 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B327" t="inlineStr"/>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Share-based payments (note 14)</t>
+          <t>Consolidated Statements of Loss and Comprehensive Loss</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
-      <c r="E327" s="5" t="n">
-        <v>1.230784</v>
-      </c>
-      <c r="F327" s="5" t="n">
-        <v>0.475137</v>
-      </c>
-      <c r="G327" s="5" t="n">
-        <v>0.189879</v>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -34694,11 +34608,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L327" s="5" t="n">
-        <v>0.07388599999999999</v>
-      </c>
-      <c r="M327" s="5" t="n">
-        <v>0.121214</v>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N327" t="inlineStr">
         <is>
@@ -34715,10 +34633,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q327" s="5" t="n">
+        <v>7e-06</v>
       </c>
       <c r="R327" t="inlineStr">
         <is>
@@ -34732,14 +34648,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B328" t="inlineStr"/>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation assets</t>
+          <t>Statements of Loss and Comprehensive Loss</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -34748,44 +34660,56 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F328" s="5" t="n">
-        <v>1.147766</v>
-      </c>
-      <c r="G328" s="5" t="n">
-        <v>3.861912</v>
-      </c>
-      <c r="H328" s="5" t="n">
-        <v>3.472037</v>
-      </c>
-      <c r="I328" s="5" t="n">
-        <v>0.006334</v>
-      </c>
-      <c r="J328" s="5" t="n">
-        <v>0.6786489999999999</v>
-      </c>
-      <c r="K328" s="5" t="n">
-        <v>0.080598</v>
-      </c>
-      <c r="L328" s="5" t="n">
-        <v>0.321354</v>
-      </c>
-      <c r="M328" s="5" t="n">
-        <v>1.781909</v>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N328" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O328" s="5" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="P328" s="5" t="n">
+        <v>4e-06</v>
       </c>
       <c r="Q328" t="inlineStr">
         <is>
@@ -34804,14 +34728,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B329" t="inlineStr"/>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Foreign currency translation adjustment</t>
+          <t>Statements of Income (loss) and Comprehensive Income (loss)</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -34820,34 +34740,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F329" s="5" t="n">
-        <v>-0.110503</v>
-      </c>
-      <c r="G329" s="5" t="n">
-        <v>-0.00533</v>
-      </c>
-      <c r="H329" s="5" t="n">
-        <v>-0.064266</v>
-      </c>
-      <c r="I329" s="5" t="n">
-        <v>-0.01507</v>
-      </c>
-      <c r="J329" s="5" t="n">
-        <v>-0.001649</v>
-      </c>
-      <c r="K329" s="5" t="n">
-        <v>-0.006449</v>
-      </c>
-      <c r="L329" s="5" t="n">
-        <v>0.008296</v>
-      </c>
-      <c r="M329" s="5" t="n">
-        <v>-0.018452</v>
-      </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N329" s="5" t="n">
+        <v>4e-06</v>
       </c>
       <c r="O329" t="inlineStr">
         <is>
@@ -34878,31 +34812,23 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Share-based payments (note 14)</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" s="5" t="n">
-        <v>0.0236</v>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.230784</v>
+      </c>
+      <c r="F330" s="5" t="n">
+        <v>0.475137</v>
+      </c>
+      <c r="G330" s="5" t="n">
+        <v>0.189879</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -34914,17 +34840,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J330" s="5" t="n">
-        <v>0.001656</v>
-      </c>
-      <c r="K330" s="5" t="n">
-        <v>0.00346</v>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L330" s="5" t="n">
-        <v>0.009785</v>
+        <v>0.07388599999999999</v>
       </c>
       <c r="M330" s="5" t="n">
-        <v>0.012</v>
+        <v>0.121214</v>
       </c>
       <c r="N330" t="inlineStr">
         <is>
@@ -34960,12 +34890,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Gain on sale or option of exploration and evaluation assets</t>
+          <t>Write-down of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -34974,39 +34904,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F331" s="5" t="n">
+        <v>1.147766</v>
+      </c>
+      <c r="G331" s="5" t="n">
+        <v>3.861912</v>
+      </c>
+      <c r="H331" s="5" t="n">
+        <v>3.472037</v>
+      </c>
+      <c r="I331" s="5" t="n">
+        <v>0.006334</v>
+      </c>
+      <c r="J331" s="5" t="n">
+        <v>0.6786489999999999</v>
       </c>
       <c r="K331" s="5" t="n">
-        <v>3.032282</v>
+        <v>0.080598</v>
       </c>
       <c r="L331" s="5" t="n">
-        <v>0.135766</v>
+        <v>0.321354</v>
       </c>
       <c r="M331" s="5" t="n">
-        <v>0.22684</v>
+        <v>1.781909</v>
       </c>
       <c r="N331" t="inlineStr">
         <is>
@@ -35042,12 +34962,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Gain on disposal of property and equipment</t>
+          <t>Foreign currency translation adjustment</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -35056,39 +34976,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F332" s="5" t="n">
+        <v>-0.110503</v>
+      </c>
+      <c r="G332" s="5" t="n">
+        <v>-0.00533</v>
+      </c>
+      <c r="H332" s="5" t="n">
+        <v>-0.064266</v>
+      </c>
+      <c r="I332" s="5" t="n">
+        <v>-0.01507</v>
+      </c>
+      <c r="J332" s="5" t="n">
+        <v>-0.001649</v>
       </c>
       <c r="K332" s="5" t="n">
-        <v>0.001676</v>
+        <v>-0.006449</v>
       </c>
       <c r="L332" s="5" t="n">
-        <v>0.002567</v>
+        <v>0.008296</v>
       </c>
       <c r="M332" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.018452</v>
       </c>
       <c r="N332" t="inlineStr">
         <is>
@@ -35129,14 +35039,16 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Income (loss) before deferred tax recovery</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E333" s="5" t="n">
+        <v>0.0236</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -35159,16 +35071,16 @@
         </is>
       </c>
       <c r="J333" s="5" t="n">
-        <v>-2.260958</v>
+        <v>0.001656</v>
       </c>
       <c r="K333" s="5" t="n">
-        <v>1.962785</v>
+        <v>0.00346</v>
       </c>
       <c r="L333" s="5" t="n">
-        <v>-1.330133</v>
+        <v>0.009785</v>
       </c>
       <c r="M333" s="5" t="n">
-        <v>3.408699</v>
+        <v>0.012</v>
       </c>
       <c r="N333" t="inlineStr">
         <is>
@@ -35209,7 +35121,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Deferred tax recovery – flow-through (note 9(e))</t>
+          <t>Gain on sale or option of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -35243,18 +35155,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K334" s="5" t="n">
+        <v>3.032282</v>
+      </c>
+      <c r="L334" s="5" t="n">
+        <v>0.135766</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.02652</v>
+        <v>0.22684</v>
       </c>
       <c r="N334" t="inlineStr">
         <is>
@@ -35295,14 +35203,10 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Income (loss) and comprehensive income (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on disposal of property and equipment</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -35328,17 +35232,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J335" s="5" t="n">
-        <v>-2.220958</v>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K335" s="5" t="n">
-        <v>2.073348</v>
+        <v>0.001676</v>
       </c>
       <c r="L335" s="5" t="n">
-        <v>-1.330133</v>
+        <v>0.002567</v>
       </c>
       <c r="M335" s="5" t="n">
-        <v>3.435219</v>
+        <v>0.001</v>
       </c>
       <c r="N335" t="inlineStr">
         <is>
@@ -35379,7 +35285,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>– basic and diluted (note 12)</t>
+          <t>Income (loss) before deferred tax recovery</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -35408,21 +35314,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J336" s="5" t="n">
+        <v>-2.260958</v>
+      </c>
+      <c r="K336" s="5" t="n">
+        <v>1.962785</v>
       </c>
       <c r="L336" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-1.330133</v>
       </c>
       <c r="M336" s="5" t="n">
-        <v>4e-08</v>
+        <v>3.408699</v>
       </c>
       <c r="N336" t="inlineStr">
         <is>
@@ -35463,18 +35365,24 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding – basic and diluted</t>
+          <t>Deferred tax recovery – flow-through (note 9(e))</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
-      <c r="E337" s="5" t="n">
-        <v>76.281509</v>
-      </c>
-      <c r="F337" s="5" t="n">
-        <v>75.71608999999999</v>
-      </c>
-      <c r="G337" s="5" t="n">
-        <v>75.798894</v>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
@@ -35486,17 +35394,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J337" s="5" t="n">
-        <v>78.720552</v>
-      </c>
-      <c r="K337" s="5" t="n">
-        <v>82.301613</v>
-      </c>
-      <c r="L337" s="5" t="n">
-        <v>84.050997</v>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M337" s="5" t="n">
-        <v>85.96580400000001</v>
+        <v>0.02652</v>
       </c>
       <c r="N337" t="inlineStr">
         <is>
@@ -35532,15 +35446,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Share-based payments (note 12)</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>Income (loss) and comprehensive income (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -35551,28 +35469,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G338" s="5" t="n">
-        <v>0.189879</v>
-      </c>
-      <c r="H338" s="5" t="n">
-        <v>0.102388</v>
-      </c>
-      <c r="I338" s="5" t="n">
-        <v>0.06499099999999999</v>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J338" s="5" t="n">
-        <v>0.005783</v>
+        <v>-2.220958</v>
       </c>
       <c r="K338" s="5" t="n">
-        <v>0.071435</v>
+        <v>2.073348</v>
       </c>
       <c r="L338" s="5" t="n">
-        <v>0.07388599999999999</v>
-      </c>
-      <c r="M338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.330133</v>
+      </c>
+      <c r="M338" s="5" t="n">
+        <v>3.435219</v>
       </c>
       <c r="N338" t="inlineStr">
         <is>
@@ -35608,43 +35530,55 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Depreciation expense</t>
+          <t>– basic and diluted (note 12)</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
-      <c r="E339" s="5" t="n">
-        <v>0.052582</v>
-      </c>
-      <c r="F339" s="5" t="n">
-        <v>0.038526</v>
-      </c>
-      <c r="G339" s="5" t="n">
-        <v>0.03239</v>
-      </c>
-      <c r="H339" s="5" t="n">
-        <v>0.034998</v>
-      </c>
-      <c r="I339" s="5" t="n">
-        <v>0.02922</v>
-      </c>
-      <c r="J339" s="5" t="n">
-        <v>0.03039</v>
-      </c>
-      <c r="K339" s="5" t="n">
-        <v>0.028114</v>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L339" s="5" t="n">
-        <v>0.023477</v>
-      </c>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="M339" s="5" t="n">
+        <v>4e-08</v>
       </c>
       <c r="N339" t="inlineStr">
         <is>
@@ -35685,24 +35619,18 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Gain on sale of long-term investments</t>
+          <t>Weighted average shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E340" s="5" t="n">
+        <v>76.281509</v>
+      </c>
+      <c r="F340" s="5" t="n">
+        <v>75.71608999999999</v>
+      </c>
+      <c r="G340" s="5" t="n">
+        <v>75.798894</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
@@ -35715,18 +35643,16 @@
         </is>
       </c>
       <c r="J340" s="5" t="n">
-        <v>0.003842</v>
+        <v>78.720552</v>
       </c>
       <c r="K340" s="5" t="n">
-        <v>0.106281</v>
+        <v>82.301613</v>
       </c>
       <c r="L340" s="5" t="n">
-        <v>0.097265</v>
-      </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>84.050997</v>
+      </c>
+      <c r="M340" s="5" t="n">
+        <v>85.96580400000001</v>
       </c>
       <c r="N340" t="inlineStr">
         <is>
@@ -35762,12 +35688,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Deferred tax recovery – flow-through (note 8(e))</t>
+          <t>Share-based payments (note 12)</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -35781,31 +35707,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G341" s="5" t="n">
+        <v>0.189879</v>
+      </c>
+      <c r="H341" s="5" t="n">
+        <v>0.102388</v>
+      </c>
+      <c r="I341" s="5" t="n">
+        <v>0.06499099999999999</v>
       </c>
       <c r="J341" s="5" t="n">
-        <v>0.04</v>
+        <v>0.005783</v>
       </c>
       <c r="K341" s="5" t="n">
-        <v>0.110563</v>
-      </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.071435</v>
+      </c>
+      <c r="L341" s="5" t="n">
+        <v>0.07388599999999999</v>
       </c>
       <c r="M341" t="inlineStr">
         <is>
@@ -35846,48 +35764,38 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>– basic and diluted (note 10)</t>
+          <t>Depreciation expense</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E342" s="5" t="n">
+        <v>0.052582</v>
+      </c>
+      <c r="F342" s="5" t="n">
+        <v>0.038526</v>
+      </c>
+      <c r="G342" s="5" t="n">
+        <v>0.03239</v>
+      </c>
+      <c r="H342" s="5" t="n">
+        <v>0.034998</v>
+      </c>
+      <c r="I342" s="5" t="n">
+        <v>0.02922</v>
       </c>
       <c r="J342" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.03039</v>
       </c>
       <c r="K342" s="5" t="n">
-        <v>3e-08</v>
+        <v>0.028114</v>
       </c>
       <c r="L342" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.023477</v>
       </c>
       <c r="M342" t="inlineStr">
         <is>
@@ -35933,7 +35841,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Gain on sale or option of exploration and evaluation assets (note 7(c))</t>
+          <t>Gain on sale of long-term investments</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -35963,15 +35871,13 @@
         </is>
       </c>
       <c r="J343" s="5" t="n">
-        <v>0.07668700000000001</v>
+        <v>0.003842</v>
       </c>
       <c r="K343" s="5" t="n">
-        <v>3.032282</v>
-      </c>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.106281</v>
+      </c>
+      <c r="L343" s="5" t="n">
+        <v>0.097265</v>
       </c>
       <c r="M343" t="inlineStr">
         <is>
@@ -36017,7 +35923,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Gain (loss) on disposal of property and equipment</t>
+          <t>Deferred tax recovery – flow-through (note 8(e))</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -36047,10 +35953,10 @@
         </is>
       </c>
       <c r="J344" s="5" t="n">
-        <v>-9.7e-05</v>
+        <v>0.04</v>
       </c>
       <c r="K344" s="5" t="n">
-        <v>0.001676</v>
+        <v>0.110563</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -36096,12 +36002,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Other income total</t>
+          <t>– basic and diluted (note 10)</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -36125,21 +36031,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I345" s="5" t="n">
-        <v>0.014648</v>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J345" s="5" t="n">
-        <v>0.001656</v>
-      </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3e-08</v>
+      </c>
+      <c r="K345" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="L345" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="M345" t="inlineStr">
         <is>
@@ -36180,12 +36084,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>(551,951)           383,942loss investments</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Loss on disposal of property and equipment</t>
+          <t>Gain on sale or option of exploration and evaluation assets (note 7(c))</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
@@ -36209,16 +36113,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I346" s="5" t="n">
-        <v>-0.004546</v>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J346" s="5" t="n">
-        <v>-9.7e-05</v>
-      </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07668700000000001</v>
+      </c>
+      <c r="K346" s="5" t="n">
+        <v>3.032282</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -36264,12 +36168,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>(551,951)           383,942loss investments</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Gain on sale of long-term investments</t>
+          <t>Gain (loss) on disposal of property and equipment</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
@@ -36293,16 +36197,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I347" s="5" t="n">
-        <v>0.045943</v>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J347" s="5" t="n">
-        <v>0.003842</v>
-      </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9.7e-05</v>
+      </c>
+      <c r="K347" s="5" t="n">
+        <v>0.001676</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -36348,12 +36252,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>(551,951)           383,942loss investments</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>(551,951)           383,942loss investments total</t>
+          <t>Other income total</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
@@ -36378,10 +36282,10 @@
         </is>
       </c>
       <c r="I348" s="5" t="n">
-        <v>0.6592789999999999</v>
+        <v>0.014648</v>
       </c>
       <c r="J348" s="5" t="n">
-        <v>-0.431461</v>
+        <v>0.001656</v>
       </c>
       <c r="K348" t="inlineStr">
         <is>
@@ -36437,7 +36341,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Loss before deferred tax recovery</t>
+          <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
@@ -36462,10 +36366,10 @@
         </is>
       </c>
       <c r="I349" s="5" t="n">
-        <v>-0.451648</v>
+        <v>-0.004546</v>
       </c>
       <c r="J349" s="5" t="n">
-        <v>-2.260958</v>
+        <v>-9.7e-05</v>
       </c>
       <c r="K349" t="inlineStr">
         <is>
@@ -36521,7 +36425,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Deferred tax recovery – flow-through (note 8(d) and 11)</t>
+          <t>Gain on sale of long-term investments</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
@@ -36545,13 +36449,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I350" s="5" t="n">
+        <v>0.045943</v>
       </c>
       <c r="J350" s="5" t="n">
-        <v>0.04</v>
+        <v>0.003842</v>
       </c>
       <c r="K350" t="inlineStr">
         <is>
@@ -36607,14 +36509,10 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>(551,951)           383,942loss investments total</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -36636,10 +36534,10 @@
         </is>
       </c>
       <c r="I351" s="5" t="n">
-        <v>-0.451648</v>
+        <v>0.6592789999999999</v>
       </c>
       <c r="J351" s="5" t="n">
-        <v>-2.220958</v>
+        <v>-0.431461</v>
       </c>
       <c r="K351" t="inlineStr">
         <is>
@@ -36690,19 +36588,15 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss per common share</t>
+          <t>(551,951)           383,942loss investments</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>– basic and diluted (note 10)</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Loss before deferred tax recovery</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -36718,14 +36612,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H352" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I352" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.451648</v>
       </c>
       <c r="J352" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-2.260958</v>
       </c>
       <c r="K352" t="inlineStr">
         <is>
@@ -36776,19 +36672,15 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss per common share</t>
+          <t>(551,951)           383,942loss investments</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Deferred tax recovery – flow-through (note 8(d) and 11)</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>
@@ -36804,14 +36696,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H353" s="5" t="n">
-        <v>77.261735</v>
-      </c>
-      <c r="I353" s="5" t="n">
-        <v>76.912042</v>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J353" s="5" t="n">
-        <v>78.720552</v>
+        <v>0.04</v>
       </c>
       <c r="K353" t="inlineStr">
         <is>
@@ -36862,15 +36758,19 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>(551,951)           383,942loss investments</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity $ 8,890,796 (451,648) 3,500 64,991 8,507,639 (2,220,958) 200,000 (40,000) 33,750</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -36892,10 +36792,10 @@
         </is>
       </c>
       <c r="I354" s="5" t="n">
-        <v>6.486214</v>
+        <v>-0.451648</v>
       </c>
       <c r="J354" s="5" t="n">
-        <v>0.005783</v>
+        <v>-2.220958</v>
       </c>
       <c r="K354" t="inlineStr">
         <is>
@@ -36946,15 +36846,19 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>Loss and comprehensive loss per common share</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Retained earnings (deficit) $ (19,933,680) (451,648) - - (20,385,328) (2,220,958) - - -</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>– basic and diluted (note 10)</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -36970,18 +36874,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H355" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="I355" s="5" t="n">
-        <v>-22.606286</v>
-      </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="J355" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="K355" t="inlineStr">
         <is>
@@ -37032,15 +36932,19 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>Loss and comprehensive loss per common share</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Reserves $ 1,597,552 - - 64,991 1,662,543 - - - -</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>Weighted average shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -37056,16 +36960,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H356" s="5" t="n">
+        <v>77.261735</v>
       </c>
       <c r="I356" s="5" t="n">
-        <v>1.668326</v>
+        <v>76.912042</v>
       </c>
       <c r="J356" s="5" t="n">
-        <v>0.005783</v>
+        <v>78.720552</v>
       </c>
       <c r="K356" t="inlineStr">
         <is>
@@ -37121,7 +37023,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Amount $ - 3,500 - - 200,000 (40,000) 33,750 - Capital 27,226,924</t>
+          <t>Total shareholders’ equity $ 8,890,796 (451,648) 3,500 64,991 8,507,639 (2,220,958) 200,000 (40,000) 33,750</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -37146,10 +37048,10 @@
         </is>
       </c>
       <c r="I357" s="5" t="n">
-        <v>27.424174</v>
+        <v>6.486214</v>
       </c>
       <c r="J357" s="5" t="n">
-        <v>27.230424</v>
+        <v>0.005783</v>
       </c>
       <c r="K357" t="inlineStr">
         <is>
@@ -37200,12 +37102,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation assets (note 7)</t>
+          <t>Retained earnings (deficit) $ (19,933,680) (451,648) - - (20,385,328) (2,220,958) - - -</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
@@ -37224,11 +37126,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H358" s="5" t="n">
-        <v>3.472037</v>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I358" s="5" t="n">
-        <v>0.006334</v>
+        <v>-22.606286</v>
       </c>
       <c r="J358" t="inlineStr">
         <is>
@@ -37284,12 +37188,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Management fees</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Management fees total</t>
+          <t>Reserves $ 1,597,552 - - 64,991 1,662,543 - - - -</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -37308,18 +37212,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H359" s="5" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I359" s="5" t="n">
+        <v>1.668326</v>
+      </c>
+      <c r="J359" s="5" t="n">
+        <v>0.005783</v>
       </c>
       <c r="K359" t="inlineStr">
         <is>
@@ -37370,12 +37272,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>383,942         (245,510)loss investments</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Gain on disposal of exploration and evaluation assets</t>
+          <t>Amount $ - 3,500 - - 200,000 (40,000) 33,750 - Capital 27,226,924</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
@@ -37400,12 +37302,10 @@
         </is>
       </c>
       <c r="I360" s="5" t="n">
-        <v>0.119914</v>
-      </c>
-      <c r="J360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>27.424174</v>
+      </c>
+      <c r="J360" s="5" t="n">
+        <v>27.230424</v>
       </c>
       <c r="K360" t="inlineStr">
         <is>
@@ -37456,12 +37356,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>383,942         (245,510)loss investments</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Gain (loss) on disposal of property and equipment</t>
+          <t>Write-down of exploration and evaluation assets (note 7)</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -37481,10 +37381,10 @@
         </is>
       </c>
       <c r="H361" s="5" t="n">
-        <v>0.008995</v>
+        <v>3.472037</v>
       </c>
       <c r="I361" s="5" t="n">
-        <v>-0.004546</v>
+        <v>0.006334</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -37540,12 +37440,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>383,942         (245,510)loss investments</t>
+          <t>Management fees</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Gain (loss) on sale of long-term investments (note 5)</t>
+          <t>Management fees total</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -37565,10 +37465,12 @@
         </is>
       </c>
       <c r="H362" s="5" t="n">
-        <v>-0.09492100000000001</v>
-      </c>
-      <c r="I362" s="5" t="n">
-        <v>0.045943</v>
+        <v>0.035</v>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
@@ -37629,7 +37531,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>383,942         (245,510)loss investments total</t>
+          <t>Gain on disposal of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -37648,11 +37550,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H363" s="5" t="n">
-        <v>-0.153716</v>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I363" s="5" t="n">
-        <v>0.6592789999999999</v>
+        <v>0.119914</v>
       </c>
       <c r="J363" t="inlineStr">
         <is>
@@ -37713,14 +37617,10 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain (loss) on disposal of property and equipment</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
@@ -37737,10 +37637,10 @@
         </is>
       </c>
       <c r="H364" s="5" t="n">
-        <v>-4.722831</v>
+        <v>0.008995</v>
       </c>
       <c r="I364" s="5" t="n">
-        <v>-0.451648</v>
+        <v>-0.004546</v>
       </c>
       <c r="J364" t="inlineStr">
         <is>
@@ -37796,12 +37696,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>383,942         (245,510)loss investments</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity $ 13,475,324 (4,722,831) (42,585) 78,500 102,388 8,890,796 (451,648) 3,500</t>
+          <t>Gain (loss) on sale of long-term investments (note 5)</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -37821,10 +37721,10 @@
         </is>
       </c>
       <c r="H365" s="5" t="n">
-        <v>8.507638999999999</v>
+        <v>-0.09492100000000001</v>
       </c>
       <c r="I365" s="5" t="n">
-        <v>0.06499099999999999</v>
+        <v>0.045943</v>
       </c>
       <c r="J365" t="inlineStr">
         <is>
@@ -37880,12 +37780,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>383,942         (245,510)loss investments</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Retained earnings (deficit) $ (15,210,849) (4,722,831) - - (19,933,680) (451,648) -</t>
+          <t>383,942         (245,510)loss investments total</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -37905,12 +37805,10 @@
         </is>
       </c>
       <c r="H366" s="5" t="n">
-        <v>-20.385328</v>
-      </c>
-      <c r="I366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.153716</v>
+      </c>
+      <c r="I366" s="5" t="n">
+        <v>0.6592789999999999</v>
       </c>
       <c r="J366" t="inlineStr">
         <is>
@@ -37966,15 +37864,19 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>383,942         (245,510)loss investments</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Reserves $ 1,200,387 - 294,777 - 102,388 1,597,552 - -</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -37991,10 +37893,10 @@
         </is>
       </c>
       <c r="H367" s="5" t="n">
-        <v>1.662543</v>
+        <v>-4.722831</v>
       </c>
       <c r="I367" s="5" t="n">
-        <v>0.06499099999999999</v>
+        <v>-0.451648</v>
       </c>
       <c r="J367" t="inlineStr">
         <is>
@@ -38055,7 +37957,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Capital Amount $ 27,485,786 - (337,362) 78,500 - 27,226,924 - 3,500</t>
+          <t>Total shareholders’ equity $ 13,475,324 (4,722,831) (42,585) 78,500 102,388 8,890,796 (451,648) 3,500</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -38075,12 +37977,10 @@
         </is>
       </c>
       <c r="H368" s="5" t="n">
-        <v>27.230424</v>
-      </c>
-      <c r="I368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.507638999999999</v>
+      </c>
+      <c r="I368" s="5" t="n">
+        <v>0.06499099999999999</v>
       </c>
       <c r="J368" t="inlineStr">
         <is>
@@ -38136,19 +38036,15 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Management fees (note 9)</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Retained earnings (deficit) $ (15,210,849) (4,722,831) - - (19,933,680) (451,648) -</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -38159,11 +38055,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G369" s="5" t="n">
-        <v>0.046</v>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H369" s="5" t="n">
-        <v>0.035</v>
+        <v>-20.385328</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -38224,12 +38122,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Gain on sale of exploration and evaluation assets (note 5)</t>
+          <t>Reserves $ 1,200,387 - 294,777 - 102,388 1,597,552 - -</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -38243,18 +38141,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G370" s="5" t="n">
-        <v>0.590686</v>
-      </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H370" s="5" t="n">
+        <v>1.662543</v>
+      </c>
+      <c r="I370" s="5" t="n">
+        <v>0.06499099999999999</v>
       </c>
       <c r="J370" t="inlineStr">
         <is>
@@ -38310,12 +38206,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Gain on sale of property and equipment                                                     8,995</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Loss on sale of long-term investments (note 5)</t>
+          <t>Capital Amount $ 27,485,786 - (337,362) 78,500 - 27,226,924 - 3,500</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -38329,11 +38225,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G371" s="5" t="n">
-        <v>-0.242034</v>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H371" s="5" t="n">
-        <v>-0.09492100000000001</v>
+        <v>27.230424</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -38394,15 +38292,19 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Gain on sale of property and equipment                                                     8,995</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Gain on sale of property and equipment                                                     8,995 total</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr"/>
+          <t>Management fees (note 9)</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -38414,10 +38316,10 @@
         </is>
       </c>
       <c r="G372" s="5" t="n">
-        <v>0.360933</v>
+        <v>0.046</v>
       </c>
       <c r="H372" s="5" t="n">
-        <v>-0.153716</v>
+        <v>0.035</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -38478,19 +38380,15 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Gain on sale of property and equipment                                                     8,995</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Gain on sale of exploration and evaluation assets (note 5)</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -38502,10 +38400,12 @@
         </is>
       </c>
       <c r="G373" s="5" t="n">
-        <v>-4.798503</v>
-      </c>
-      <c r="H373" s="5" t="n">
-        <v>-4.722831</v>
+        <v>0.590686</v>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -38571,7 +38471,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>Loss on sale of long-term investments (note 5)</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -38586,12 +38486,10 @@
         </is>
       </c>
       <c r="G374" s="5" t="n">
-        <v>0.293456</v>
-      </c>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.242034</v>
+      </c>
+      <c r="H374" s="5" t="n">
+        <v>-0.09492100000000001</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -38657,14 +38555,10 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on sale of property and equipment                                                     8,995 total</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -38676,10 +38570,10 @@
         </is>
       </c>
       <c r="G375" s="5" t="n">
-        <v>-4.505047</v>
+        <v>0.360933</v>
       </c>
       <c r="H375" s="5" t="n">
-        <v>-4.722831</v>
+        <v>-0.153716</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -38745,12 +38639,12 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss per common share – basic and diluted (note 10)</t>
+          <t>Loss before income taxes</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -38764,10 +38658,10 @@
         </is>
       </c>
       <c r="G376" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>-4.798503</v>
       </c>
       <c r="H376" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>-4.722831</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -38833,10 +38727,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>Deferred income tax recovery</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -38848,10 +38746,12 @@
         </is>
       </c>
       <c r="G377" s="5" t="n">
-        <v>75.798894</v>
-      </c>
-      <c r="H377" s="5" t="n">
-        <v>77.261735</v>
+        <v>0.293456</v>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
@@ -38912,15 +38812,19 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>Gain on sale of property and equipment                                                     8,995</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity $ 17,679,742 (4,505,047) 126,000 (15,250) 189,879 13,475,324 (4,722,831) (42,585) 78,500</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -38932,10 +38836,10 @@
         </is>
       </c>
       <c r="G378" s="5" t="n">
-        <v>8.890796</v>
+        <v>-4.505047</v>
       </c>
       <c r="H378" s="5" t="n">
-        <v>0.102388</v>
+        <v>-4.722831</v>
       </c>
       <c r="I378" t="inlineStr">
         <is>
@@ -38996,15 +38900,19 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>Gain on sale of property and equipment                                                     8,995</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Retained earnings (deficit) $ (10,705,802) (4,505,047) - - - (15,210,849) (4,722,831) -</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>Loss and comprehensive loss per common share – basic and diluted (note 10)</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -39016,12 +38924,10 @@
         </is>
       </c>
       <c r="G379" s="5" t="n">
-        <v>-19.93368</v>
-      </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="H379" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="I379" t="inlineStr">
         <is>
@@ -39082,12 +38988,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>Gain on sale of property and equipment                                                     8,995</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Reserves $ 934,008 - - 76,500 189,879 1,200,387 - 294,777 -</t>
+          <t>Weighted average shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -39102,10 +39008,10 @@
         </is>
       </c>
       <c r="G380" s="5" t="n">
-        <v>1.597552</v>
+        <v>75.798894</v>
       </c>
       <c r="H380" s="5" t="n">
-        <v>0.102388</v>
+        <v>77.261735</v>
       </c>
       <c r="I380" t="inlineStr">
         <is>
@@ -39171,7 +39077,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Capital Amount $ 27,451,536 - 126,000 (91,750) - 27,485,786 - (337,362) 78,500</t>
+          <t>Total shareholders’ equity $ 17,679,742 (4,505,047) 126,000 (15,250) 189,879 13,475,324 (4,722,831) (42,585) 78,500</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -39186,12 +39092,10 @@
         </is>
       </c>
       <c r="G381" s="5" t="n">
-        <v>27.226924</v>
-      </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.890796</v>
+      </c>
+      <c r="H381" s="5" t="n">
+        <v>0.102388</v>
       </c>
       <c r="I381" t="inlineStr">
         <is>
@@ -39252,29 +39156,27 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Management fees (note 11)</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Retained earnings (deficit) $ (10,705,802) (4,505,047) - - - (15,210,849) (4,722,831) -</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F382" s="5" t="n">
-        <v>0.028</v>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G382" s="5" t="n">
-        <v>0.046</v>
+        <v>-19.93368</v>
       </c>
       <c r="H382" t="inlineStr">
         <is>
@@ -39340,12 +39242,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Gain on sale of exploration and evaluation assets (notes 7(vi), 9)</t>
+          <t>Reserves $ 934,008 - - 76,500 189,879 1,200,387 - 294,777 -</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -39354,16 +39256,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F383" s="5" t="n">
-        <v>0.305578</v>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G383" s="5" t="n">
-        <v>0.590686</v>
-      </c>
-      <c r="H383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.597552</v>
+      </c>
+      <c r="H383" s="5" t="n">
+        <v>0.102388</v>
       </c>
       <c r="I383" t="inlineStr">
         <is>
@@ -39424,12 +39326,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Loss on sale of long-term investments (note 7)</t>
+          <t>Capital Amount $ 27,451,536 - 126,000 (91,750) - 27,485,786 - (337,362) 78,500</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -39438,11 +39340,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F384" s="5" t="n">
-        <v>-0.066508</v>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G384" s="5" t="n">
-        <v>-0.242034</v>
+        <v>27.226924</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
@@ -39513,22 +39417,24 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
+          <t>Management fees (note 11)</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E385" s="5" t="n">
-        <v>-11.81156</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F385" s="5" t="n">
-        <v>-1.87265</v>
+        <v>0.028</v>
       </c>
       <c r="G385" s="5" t="n">
-        <v>-4.798503</v>
+        <v>0.046</v>
       </c>
       <c r="H385" t="inlineStr">
         <is>
@@ -39599,18 +39505,20 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (expense) (note 13)</t>
+          <t>Gain on sale of exploration and evaluation assets (notes 7(vi), 9)</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
-      <c r="E386" s="5" t="n">
-        <v>2.482244</v>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F386" s="5" t="n">
-        <v>-0.235157</v>
+        <v>0.305578</v>
       </c>
       <c r="G386" s="5" t="n">
-        <v>0.293456</v>
+        <v>0.590686</v>
       </c>
       <c r="H386" t="inlineStr">
         <is>
@@ -39681,22 +39589,20 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss per common share – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E387" s="5" t="n">
-        <v>-1.2e-07</v>
+          <t>Loss on sale of long-term investments (note 7)</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F387" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-0.066508</v>
       </c>
       <c r="G387" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>-0.242034</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
@@ -39762,25 +39668,27 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity $ 13,494,671 362,730 5,615,127 (1) (2,107,807) 2,750 (162,865) 475,137 17,679,742 (4,505,047) 126,000 (15,250)</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E388" s="5" t="n">
+        <v>-11.81156</v>
       </c>
       <c r="F388" s="5" t="n">
-        <v>13.475324</v>
+        <v>-1.87265</v>
       </c>
       <c r="G388" s="5" t="n">
-        <v>0.189879</v>
+        <v>-4.798503</v>
       </c>
       <c r="H388" t="inlineStr">
         <is>
@@ -39846,27 +39754,27 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>- - - - - - Retained earnings (deficit) $ (8,597,995) (2,107,807) (10,705,802) (4,505,047) - -</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deferred income tax recovery (expense) (note 13)</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E389" s="5" t="n">
+        <v>2.482244</v>
       </c>
       <c r="F389" s="5" t="n">
-        <v>-15.210849</v>
-      </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.235157</v>
+      </c>
+      <c r="G389" s="5" t="n">
+        <v>0.293456</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
@@ -39932,25 +39840,27 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>- - - 458,871 475,137 934,008 - - 76,500 189,879 1,200,387 Reserves $ 22,092,665</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss and comprehensive loss per common share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E390" s="5" t="n">
+        <v>-1.2e-07</v>
       </c>
       <c r="F390" s="5" t="n">
-        <v>-22.455395</v>
+        <v>-3e-08</v>
       </c>
       <c r="G390" s="5" t="n">
-        <v>0.36273</v>
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
@@ -40021,7 +39931,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>- - - Amount $ 1 2,750 (621,736) Capital 27,451,536 - 126,000 (91,750) - 27,485,786</t>
+          <t>Total shareholders’ equity $ 13,494,671 362,730 5,615,127 (1) (2,107,807) 2,750 (162,865) 475,137 17,679,742 (4,505,047) 126,000 (15,250)</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -40031,10 +39941,10 @@
         </is>
       </c>
       <c r="F391" s="5" t="n">
-        <v>-1e-06</v>
+        <v>13.475324</v>
       </c>
       <c r="G391" s="5" t="n">
-        <v>28.070522</v>
+        <v>0.189879</v>
       </c>
       <c r="H391" t="inlineStr">
         <is>
@@ -40100,12 +40010,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Share    1                                                                    (1)       -  -                                     statements</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Number financial - 76,273,531 - 25,000 (1,689,500) - 74,609,031 1,850,000</t>
+          <t>- - - - - - Retained earnings (deficit) $ (8,597,995) (2,107,807) (10,705,802) (4,505,047) - -</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -40115,10 +40025,12 @@
         </is>
       </c>
       <c r="F392" s="5" t="n">
-        <v>76.209031</v>
-      </c>
-      <c r="G392" s="5" t="n">
-        <v>-0.25</v>
+        <v>-15.210849</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
@@ -40184,25 +40096,25 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Write-down (recovery) of exploration and evaluation assets</t>
+          <t>- - - 458,871 475,137 934,008 - - 76,500 189,879 1,200,387 Reserves $ 22,092,665</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
-      <c r="E393" s="5" t="n">
-        <v>2.597917</v>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F393" s="5" t="n">
-        <v>1.147766</v>
-      </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-22.455395</v>
+      </c>
+      <c r="G393" s="5" t="n">
+        <v>0.36273</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
@@ -40268,29 +40180,25 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E394" s="5" t="n">
-        <v>0.272547</v>
+          <t>- - - Amount $ 1 2,750 (621,736) Capital 27,451,536 - 126,000 (91,750) - 27,485,786</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F394" s="5" t="n">
-        <v>0.093374</v>
-      </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-06</v>
+      </c>
+      <c r="G394" s="5" t="n">
+        <v>28.070522</v>
       </c>
       <c r="H394" t="inlineStr">
         <is>
@@ -40356,25 +40264,25 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Share    1                                                                    (1)       -  -                                     statements</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Gain on sale of exploration and evaluation assets</t>
+          <t>Number financial - 76,273,531 - 25,000 (1,689,500) - 74,609,031 1,850,000</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
-      <c r="E395" s="5" t="n">
-        <v>0.775</v>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F395" s="5" t="n">
-        <v>0.305578</v>
-      </c>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>76.209031</v>
+      </c>
+      <c r="G395" s="5" t="n">
+        <v>-0.25</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
@@ -40440,22 +40348,20 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Loss on sale of investments</t>
+          <t>Write-down (recovery) of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E396" s="5" t="n">
+        <v>2.597917</v>
       </c>
       <c r="F396" s="5" t="n">
-        <v>-0.066508</v>
+        <v>1.147766</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
@@ -40531,17 +40437,19 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Current income tax recovery (note 13)</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E397" s="5" t="n">
-        <v>0.40375</v>
-      </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.272547</v>
+      </c>
+      <c r="F397" s="5" t="n">
+        <v>0.093374</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
@@ -40612,20 +40520,20 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity $ 16,008.857 1 (8,925,566) 6,411,379 13,494,671 362,730 5,615,127 (1) (2,107,807) 2,750 (162,865)</t>
+          <t>Gain on sale of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
       <c r="E398" s="5" t="n">
-        <v>17.679742</v>
+        <v>0.775</v>
       </c>
       <c r="F398" s="5" t="n">
-        <v>0.475137</v>
+        <v>0.305578</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
@@ -40696,22 +40604,22 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Retained earnings (deficit) $ 327571 - (8,925,566) - (8,597,995) - - - (2,107,807) - -</t>
+          <t>Loss on sale of investments</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
-      <c r="E399" s="5" t="n">
-        <v>-10.705802</v>
-      </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F399" s="5" t="n">
+        <v>-0.066508</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -40782,22 +40690,26 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements total</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr"/>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F400" s="5" t="n">
-        <v>0.00275</v>
+          <t>Current income tax recovery (note 13)</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E400" s="5" t="n">
+        <v>0.40375</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
@@ -40873,12 +40785,12 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>- - Reserves 15,681,286 6,411,379 22,092,665 362,730 (22,455,395) 458,871</t>
+          <t>Total shareholders’ equity $ 16,008.857 1 (8,925,566) 6,411,379 13,494,671 362,730 5,615,127 (1) (2,107,807) 2,750 (162,865)</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
       <c r="E401" s="5" t="n">
-        <v>0.9340079999999999</v>
+        <v>17.679742</v>
       </c>
       <c r="F401" s="5" t="n">
         <v>0.475137</v>
@@ -40957,15 +40869,17 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Capital Amount 28,070,522</t>
+          <t>Retained earnings (deficit) $ 327571 - (8,925,566) - (8,597,995) - - - (2,107,807) - -</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
       <c r="E402" s="5" t="n">
-        <v>27.451536</v>
-      </c>
-      <c r="F402" s="5" t="n">
-        <v>-0.621736</v>
+        <v>-10.705802</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
@@ -41036,77 +40950,331 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
+          <t>See accompanying notes to the financial statements</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>See accompanying notes to the financial statements total</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F403" s="5" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>See accompanying notes to the financial statements</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>- - Reserves 15,681,286 6,411,379 22,092,665 362,730 (22,455,395) 458,871</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" s="5" t="n">
+        <v>0.9340079999999999</v>
+      </c>
+      <c r="F404" s="5" t="n">
+        <v>0.475137</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>See accompanying notes to the financial statements</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Capital Amount 28,070,522</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" s="5" t="n">
+        <v>27.451536</v>
+      </c>
+      <c r="F405" s="5" t="n">
+        <v>-0.621736</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
           <t>Share     1  1                          -      (1) -  -                                     statements</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr">
+      <c r="C406" t="inlineStr">
         <is>
           <t>Number financial - - 76,273,531 25,000</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
-      <c r="E403" s="5" t="n">
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" s="5" t="n">
         <v>74.609031</v>
       </c>
-      <c r="F403" s="5" t="n">
+      <c r="F406" s="5" t="n">
         <v>-1.6895</v>
       </c>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R403" t="inlineStr">
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
         <is>
           <t>-</t>
         </is>
